--- a/Documents/clientfiles/PackageTypeReference.xlsx
+++ b/Documents/clientfiles/PackageTypeReference.xlsx
@@ -5,18 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitLab\joboffer\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Gitlab\joboffer\Documents\clientfiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{031A3334-0821-4A96-9B30-80F0853886E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E65C268D-D240-4CD2-BD36-7359A6B3C346}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{1213133A-9C7C-4670-92AE-C0C0DD240442}"/>
+    <workbookView xWindow="2688" yWindow="2688" windowWidth="21300" windowHeight="12072" firstSheet="1" activeTab="5" xr2:uid="{1213133A-9C7C-4670-92AE-C0C0DD240442}"/>
   </bookViews>
   <sheets>
     <sheet name="Clause for Letters" sheetId="1" r:id="rId1"/>
     <sheet name="NON KP" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="5" r:id="rId5"/>
+    <sheet name="INSERT" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="73">
   <si>
     <t>Email Body</t>
   </si>
@@ -233,6 +235,36 @@
   </si>
   <si>
     <t>3,000 Monthly or 36,000 Annually</t>
+  </si>
+  <si>
+    <t>Office Based No Car</t>
+  </si>
+  <si>
+    <t>Office With Car</t>
+  </si>
+  <si>
+    <t>Field Commercial</t>
+  </si>
+  <si>
+    <t>Office Commercial</t>
+  </si>
+  <si>
+    <t>With/Without Hazard</t>
+  </si>
+  <si>
+    <t>With Pharmacist Allowance</t>
+  </si>
+  <si>
+    <t>Non- Regular</t>
+  </si>
+  <si>
+    <t>Office Commercial - ULCH</t>
+  </si>
+  <si>
+    <t>Office Commercial - ULSSI</t>
+  </si>
+  <si>
+    <t>Office Commercial - ULCH Probationar</t>
   </si>
 </sst>
 </file>
@@ -614,19 +646,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -634,6 +654,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1011,13 +1043,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3FF3A112-F506-4B63-A62C-EC993A7D564A}">
   <dimension ref="A2:B14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27.453125" customWidth="1"/>
-    <col min="2" max="2" width="58.26953125" customWidth="1"/>
+    <col min="1" max="1" width="27.44140625" customWidth="1"/>
+    <col min="2" max="2" width="58.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1025,7 +1057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
@@ -1033,7 +1065,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -1041,7 +1073,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>6</v>
       </c>
@@ -1049,7 +1081,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -1057,7 +1089,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="58" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -1065,7 +1097,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>12</v>
       </c>
@@ -1073,7 +1105,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -1081,7 +1113,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>16</v>
       </c>
@@ -1089,7 +1121,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>18</v>
       </c>
@@ -1097,7 +1129,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -1105,7 +1137,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>22</v>
       </c>
@@ -1113,7 +1145,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>24</v>
       </c>
@@ -1129,33 +1161,33 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3129B84D-D8F8-4718-8094-B223A15AC3B6}">
   <dimension ref="A1:U16"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="0" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="46.54296875" style="29" customWidth="1"/>
-    <col min="2" max="2" width="8.7265625" style="28" customWidth="1"/>
-    <col min="3" max="3" width="27.453125" style="28" customWidth="1"/>
-    <col min="4" max="4" width="8.7265625" style="28" customWidth="1"/>
-    <col min="5" max="5" width="27.453125" style="28" customWidth="1"/>
-    <col min="6" max="6" width="6.54296875" style="28" customWidth="1"/>
-    <col min="7" max="7" width="25.81640625" style="28" customWidth="1"/>
-    <col min="8" max="8" width="7.81640625" style="28" customWidth="1"/>
-    <col min="9" max="9" width="27.1796875" style="28" customWidth="1"/>
-    <col min="10" max="10" width="7.81640625" style="28" customWidth="1"/>
-    <col min="11" max="11" width="27.1796875" style="28" customWidth="1"/>
-    <col min="12" max="12" width="7.81640625" style="28" customWidth="1"/>
-    <col min="13" max="13" width="27.1796875" style="28" customWidth="1"/>
-    <col min="14" max="14" width="7.81640625" style="28" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="27.1796875" style="28" hidden="1" customWidth="1"/>
-    <col min="16" max="16" width="6.1796875" style="28" customWidth="1"/>
+    <col min="1" max="1" width="46.5546875" style="29" customWidth="1"/>
+    <col min="2" max="2" width="8.77734375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="27.44140625" style="28" customWidth="1"/>
+    <col min="4" max="4" width="8.77734375" style="28" customWidth="1"/>
+    <col min="5" max="5" width="27.44140625" style="28" customWidth="1"/>
+    <col min="6" max="6" width="6.5546875" style="28" customWidth="1"/>
+    <col min="7" max="7" width="25.77734375" style="28" customWidth="1"/>
+    <col min="8" max="8" width="7.77734375" style="28" customWidth="1"/>
+    <col min="9" max="9" width="27.21875" style="28" customWidth="1"/>
+    <col min="10" max="10" width="7.77734375" style="28" customWidth="1"/>
+    <col min="11" max="11" width="27.21875" style="28" customWidth="1"/>
+    <col min="12" max="12" width="7.77734375" style="28" customWidth="1"/>
+    <col min="13" max="13" width="27.21875" style="28" customWidth="1"/>
+    <col min="14" max="14" width="7.77734375" style="28" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="27.21875" style="28" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="6.21875" style="28" customWidth="1"/>
     <col min="17" max="17" width="28" style="28" customWidth="1"/>
     <col min="18" max="18" width="7" style="28" customWidth="1"/>
-    <col min="19" max="19" width="33.453125" style="28" customWidth="1"/>
+    <col min="19" max="19" width="33.44140625" style="28" customWidth="1"/>
     <col min="20" max="20" width="7" style="28" customWidth="1"/>
-    <col min="21" max="21" width="27.81640625" style="28" customWidth="1"/>
-    <col min="22" max="16384" width="8.7265625" hidden="1"/>
+    <col min="21" max="21" width="27.77734375" style="28" customWidth="1"/>
+    <col min="22" max="16384" width="8.77734375" hidden="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="6" customFormat="1" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:21" s="6" customFormat="1" ht="18" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>26</v>
       </c>
@@ -1180,53 +1212,53 @@
       <c r="T1" s="5"/>
       <c r="U1" s="5"/>
     </row>
-    <row r="2" spans="1:21" s="8" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:21" s="8" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="36"/>
-      <c r="D2" s="35" t="s">
+      <c r="C2" s="38"/>
+      <c r="D2" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="35"/>
-      <c r="F2" s="36" t="s">
+      <c r="E2" s="39"/>
+      <c r="F2" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="36"/>
-      <c r="H2" s="35" t="s">
+      <c r="G2" s="38"/>
+      <c r="H2" s="39" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="35"/>
-      <c r="J2" s="36" t="s">
+      <c r="I2" s="39"/>
+      <c r="J2" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="K2" s="36"/>
-      <c r="L2" s="36" t="s">
+      <c r="K2" s="38"/>
+      <c r="L2" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="M2" s="36"/>
-      <c r="N2" s="35" t="s">
+      <c r="M2" s="38"/>
+      <c r="N2" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="O2" s="35"/>
-      <c r="P2" s="36" t="s">
+      <c r="O2" s="39"/>
+      <c r="P2" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="Q2" s="36"/>
-      <c r="R2" s="35" t="s">
+      <c r="Q2" s="38"/>
+      <c r="R2" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="35"/>
-      <c r="T2" s="36" t="s">
+      <c r="S2" s="39"/>
+      <c r="T2" s="38" t="s">
         <v>37</v>
       </c>
-      <c r="U2" s="36"/>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A3" s="37"/>
+      <c r="U2" s="38"/>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="35"/>
       <c r="B3" s="9" t="s">
         <v>38</v>
       </c>
@@ -1288,8 +1320,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A4" s="38"/>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4" s="40"/>
       <c r="B4" s="13" t="s">
         <v>38</v>
       </c>
@@ -1351,8 +1383,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A5" s="39"/>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5" s="41"/>
       <c r="B5" s="16" t="s">
         <v>38</v>
       </c>
@@ -1414,8 +1446,8 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A6" s="37"/>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6" s="35"/>
       <c r="B6" s="20" t="s">
         <v>38</v>
       </c>
@@ -1477,8 +1509,8 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A7" s="40"/>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7" s="36"/>
       <c r="B7" s="24" t="s">
         <v>38</v>
       </c>
@@ -1540,8 +1572,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A8" s="40"/>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8" s="36"/>
       <c r="B8" s="24" t="s">
         <v>38</v>
       </c>
@@ -1603,8 +1635,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A9" s="40"/>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9" s="36"/>
       <c r="B9" s="13" t="s">
         <v>39</v>
       </c>
@@ -1666,8 +1698,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A10" s="40"/>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10" s="36"/>
       <c r="B10" s="13" t="s">
         <v>38</v>
       </c>
@@ -1729,8 +1761,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A11" s="40"/>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11" s="36"/>
       <c r="B11" s="13" t="s">
         <v>39</v>
       </c>
@@ -1792,8 +1824,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A12" s="40"/>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12" s="36"/>
       <c r="B12" s="13" t="s">
         <v>39</v>
       </c>
@@ -1855,8 +1887,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A13" s="40"/>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13" s="36"/>
       <c r="B13" s="13" t="s">
         <v>39</v>
       </c>
@@ -1918,8 +1950,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A14" s="41"/>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14" s="37"/>
       <c r="B14" s="16" t="s">
         <v>39</v>
       </c>
@@ -1981,7 +2013,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A15" s="27" t="s">
         <v>40</v>
       </c>
@@ -2016,7 +2048,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="C16" s="28" t="s">
         <v>50</v>
       </c>
@@ -2032,11 +2064,6 @@
     </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="A6:A14"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
     <mergeCell ref="N2:O2"/>
     <mergeCell ref="P2:Q2"/>
     <mergeCell ref="R2:S2"/>
@@ -2044,6 +2071,11 @@
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:M2"/>
+    <mergeCell ref="A6:A14"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:B14 D3:D14 F3:F14 H3:H14 J3:J14 N3:N14 P3:P14 R3:R14 T3:T14">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
@@ -2068,13 +2100,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{727851F6-C9AF-4013-B1AD-0237A327AB3A}">
   <dimension ref="A1:F12"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="30.81640625" customWidth="1"/>
-    <col min="2" max="2" width="47.54296875" customWidth="1"/>
+    <col min="1" max="1" width="30.77734375" customWidth="1"/>
+    <col min="2" max="2" width="47.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="30" t="s">
         <v>2</v>
       </c>
@@ -2082,7 +2114,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="31" t="s">
         <v>4</v>
       </c>
@@ -2097,7 +2129,7 @@
         <v>insert into PckgTempHasItms(TempId,ItemId) select 1,Id from PckgItems;</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="32" t="s">
         <v>6</v>
       </c>
@@ -2112,7 +2144,7 @@
         <v>insert into PckgTempHasItms(TempId,ItemId) select 2,Id from PckgItems;</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="21" t="s">
         <v>8</v>
       </c>
@@ -2127,7 +2159,7 @@
         <v>insert into PckgTempHasItms(TempId,ItemId) select 3,Id from PckgItems;</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="33" t="s">
         <v>10</v>
       </c>
@@ -2142,7 +2174,7 @@
         <v>insert into PckgTempHasItms(TempId,ItemId) select 4,Id from PckgItems;</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="33" t="s">
         <v>12</v>
       </c>
@@ -2157,7 +2189,7 @@
         <v>insert into PckgTempHasItms(TempId,ItemId) select 5,Id from PckgItems;</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>14</v>
       </c>
@@ -2172,7 +2204,7 @@
         <v>insert into PckgTempHasItms(TempId,ItemId) select 6,Id from PckgItems;</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="31" t="s">
         <v>16</v>
       </c>
@@ -2187,7 +2219,7 @@
         <v>insert into PckgTempHasItms(TempId,ItemId) select 7,Id from PckgItems;</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="31" t="s">
         <v>18</v>
       </c>
@@ -2202,7 +2234,7 @@
         <v>insert into PckgTempHasItms(TempId,ItemId) select 8,Id from PckgItems;</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="31" t="s">
         <v>20</v>
       </c>
@@ -2217,7 +2249,7 @@
         <v>insert into PckgTempHasItms(TempId,ItemId) select 9,Id from PckgItems;</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="31" t="s">
         <v>22</v>
       </c>
@@ -2232,7 +2264,7 @@
         <v>insert into PckgTempHasItms(TempId,ItemId) select 10,Id from PckgItems;</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="32" t="s">
         <v>24</v>
       </c>
@@ -2248,14 +2280,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DCE702D9-2A3C-47C5-8329-1AA0743071AC}">
   <dimension ref="B5:E14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="37.6328125" customWidth="1"/>
-    <col min="3" max="3" width="32.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="96.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.6640625" customWidth="1"/>
+    <col min="3" max="3" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="96.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>28</v>
       </c>
@@ -2268,7 +2300,7 @@
         <v>insert into PckgTemp(TempName,CreatedAt,CreatedBy) values('Office Based No Car',getdate(),1);</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>29</v>
       </c>
@@ -2281,7 +2313,7 @@
         <v>insert into PckgTemp(TempName,CreatedAt,CreatedBy) values('Office With Car',getdate(),1);</v>
       </c>
     </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>30</v>
       </c>
@@ -2294,7 +2326,7 @@
         <v>insert into PckgTemp(TempName,CreatedAt,CreatedBy) values('Field Commercial',getdate(),1);</v>
       </c>
     </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>31</v>
       </c>
@@ -2307,7 +2339,7 @@
         <v>insert into PckgTemp(TempName,CreatedAt,CreatedBy) values('Office Commercial',getdate(),1);</v>
       </c>
     </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>32</v>
       </c>
@@ -2320,7 +2352,7 @@
         <v>insert into PckgTemp(TempName,CreatedAt,CreatedBy) values('Office Commercial - Ulch',getdate(),1);</v>
       </c>
     </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>33</v>
       </c>
@@ -2333,7 +2365,7 @@
         <v>insert into PckgTemp(TempName,CreatedAt,CreatedBy) values('Office Commercial - Ulssi',getdate(),1);</v>
       </c>
     </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>34</v>
       </c>
@@ -2346,7 +2378,7 @@
         <v>insert into PckgTemp(TempName,CreatedAt,CreatedBy) values('Office Commercial - Ulch Probationary',getdate(),1);</v>
       </c>
     </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>35</v>
       </c>
@@ -2359,7 +2391,7 @@
         <v>insert into PckgTemp(TempName,CreatedAt,CreatedBy) values('With/Without Hazard',getdate(),1);</v>
       </c>
     </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>36</v>
       </c>
@@ -2372,7 +2404,7 @@
         <v>insert into PckgTemp(TempName,CreatedAt,CreatedBy) values('With Pharmacist Allowance',getdate(),1);</v>
       </c>
     </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>37</v>
       </c>
@@ -2383,6 +2415,849 @@
       <c r="E14" t="str">
         <f t="shared" si="1"/>
         <v>insert into PckgTemp(TempName,CreatedAt,CreatedBy) values('Non- Regular',getdate(),1);</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BA90D83-D9B1-48C8-BF46-7D213E609284}">
+  <dimension ref="B3:D12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="32.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="135.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" t="str">
+        <f>"insert into CompanyCompensation(CompanyId,CmpnyCmpnstnName,IsActive,CreatedAt,CreatedBy) values(1,'"&amp;B3&amp;"',1,getdate(),1);"</f>
+        <v>insert into CompanyCompensation(CompanyId,CmpnyCmpnstnName,IsActive,CreatedAt,CreatedBy) values(1,'Office Based No Car',1,getdate(),1);</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" t="str">
+        <f t="shared" ref="D4:D12" si="0">"insert into CompanyCompensation(CompanyId,CmpnyCmpnstnName,IsActive,CreatedAt,CreatedBy) values(1,'"&amp;B4&amp;"',1,getdate(),1);"</f>
+        <v>insert into CompanyCompensation(CompanyId,CmpnyCmpnstnName,IsActive,CreatedAt,CreatedBy) values(1,'Office With Car',1,getdate(),1);</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into CompanyCompensation(CompanyId,CmpnyCmpnstnName,IsActive,CreatedAt,CreatedBy) values(1,'Field Commercial',1,getdate(),1);</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into CompanyCompensation(CompanyId,CmpnyCmpnstnName,IsActive,CreatedAt,CreatedBy) values(1,'Office Commercial',1,getdate(),1);</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="D7" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into CompanyCompensation(CompanyId,CmpnyCmpnstnName,IsActive,CreatedAt,CreatedBy) values(1,'Office Commercial - ULCH',1,getdate(),1);</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into CompanyCompensation(CompanyId,CmpnyCmpnstnName,IsActive,CreatedAt,CreatedBy) values(1,'Office Commercial - ULSSI',1,getdate(),1);</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into CompanyCompensation(CompanyId,CmpnyCmpnstnName,IsActive,CreatedAt,CreatedBy) values(1,'Office Commercial - ULCH Probationar',1,getdate(),1);</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into CompanyCompensation(CompanyId,CmpnyCmpnstnName,IsActive,CreatedAt,CreatedBy) values(1,'With/Without Hazard',1,getdate(),1);</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into CompanyCompensation(CompanyId,CmpnyCmpnstnName,IsActive,CreatedAt,CreatedBy) values(1,'With Pharmacist Allowance',1,getdate(),1);</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" t="str">
+        <f t="shared" si="0"/>
+        <v>insert into CompanyCompensation(CompanyId,CmpnyCmpnstnName,IsActive,CreatedAt,CreatedBy) values(1,'Non- Regular',1,getdate(),1);</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D35D918-D969-499D-A8DB-3D0A03CA9445}">
+  <dimension ref="B2:C104"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.6640625" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21.6640625" customWidth="1"/>
+    <col min="11" max="11" width="18.77734375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.6640625" customWidth="1"/>
+    <col min="14" max="14" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="21.6640625" customWidth="1"/>
+    <col min="17" max="17" width="27.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="21.6640625" customWidth="1"/>
+    <col min="20" max="20" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="21.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B14" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B18" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C19" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C22" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B24" t="s">
+        <v>38</v>
+      </c>
+      <c r="C24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C25" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B27" t="s">
+        <v>39</v>
+      </c>
+      <c r="C27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>39</v>
+      </c>
+      <c r="C28" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B32" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C34" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>38</v>
+      </c>
+      <c r="C36" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B37" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C38" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B39" t="s">
+        <v>38</v>
+      </c>
+      <c r="C39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B40" t="s">
+        <v>39</v>
+      </c>
+      <c r="C40" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B41" t="s">
+        <v>39</v>
+      </c>
+      <c r="C41" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B42" t="s">
+        <v>38</v>
+      </c>
+      <c r="C42" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B43" t="s">
+        <v>39</v>
+      </c>
+      <c r="C43" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B44" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B47" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B48" t="s">
+        <v>38</v>
+      </c>
+      <c r="C48" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B49" t="s">
+        <v>38</v>
+      </c>
+      <c r="C49" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B50" t="s">
+        <v>38</v>
+      </c>
+      <c r="C50" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B51" t="s">
+        <v>38</v>
+      </c>
+      <c r="C51" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B52" t="s">
+        <v>38</v>
+      </c>
+      <c r="C52" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B53" t="s">
+        <v>38</v>
+      </c>
+      <c r="C53" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B54" t="s">
+        <v>38</v>
+      </c>
+      <c r="C54" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B55" t="s">
+        <v>39</v>
+      </c>
+      <c r="C55" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B56" t="s">
+        <v>39</v>
+      </c>
+      <c r="C56" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B57" t="s">
+        <v>38</v>
+      </c>
+      <c r="C57" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B58" t="s">
+        <v>39</v>
+      </c>
+      <c r="C58" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B59" t="s">
+        <v>39</v>
+      </c>
+      <c r="C59" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B62" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B63" t="s">
+        <v>38</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B64" t="s">
+        <v>38</v>
+      </c>
+      <c r="C64" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B65" t="s">
+        <v>38</v>
+      </c>
+      <c r="C65" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B66" t="s">
+        <v>38</v>
+      </c>
+      <c r="C66" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B67" t="s">
+        <v>38</v>
+      </c>
+      <c r="C67" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B68" t="s">
+        <v>38</v>
+      </c>
+      <c r="C68" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B69" t="s">
+        <v>39</v>
+      </c>
+      <c r="C69" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B70" t="s">
+        <v>39</v>
+      </c>
+      <c r="C70" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B71" t="s">
+        <v>39</v>
+      </c>
+      <c r="C71" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B72" t="s">
+        <v>39</v>
+      </c>
+      <c r="C72" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B73" t="s">
+        <v>38</v>
+      </c>
+      <c r="C73" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B74" t="s">
+        <v>39</v>
+      </c>
+      <c r="C74" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B77" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B78" t="s">
+        <v>38</v>
+      </c>
+      <c r="C78" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
+        <v>38</v>
+      </c>
+      <c r="C79" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B80" t="s">
+        <v>38</v>
+      </c>
+      <c r="C80" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B81" t="s">
+        <v>38</v>
+      </c>
+      <c r="C81" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B82" t="s">
+        <v>38</v>
+      </c>
+      <c r="C82" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B83" t="s">
+        <v>38</v>
+      </c>
+      <c r="C83" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B84" t="s">
+        <v>39</v>
+      </c>
+      <c r="C84" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B85" t="s">
+        <v>39</v>
+      </c>
+      <c r="C85" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="86" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B86" t="s">
+        <v>39</v>
+      </c>
+      <c r="C86" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B87" t="s">
+        <v>39</v>
+      </c>
+      <c r="C87" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B88" t="s">
+        <v>39</v>
+      </c>
+      <c r="C88" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B89" t="s">
+        <v>38</v>
+      </c>
+      <c r="C89" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="92" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B92" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="93" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B93" t="s">
+        <v>38</v>
+      </c>
+      <c r="C93" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="94" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B94" t="s">
+        <v>38</v>
+      </c>
+      <c r="C94" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B95" t="s">
+        <v>39</v>
+      </c>
+      <c r="C95" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B96" t="s">
+        <v>39</v>
+      </c>
+      <c r="C96" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="97" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B97" t="s">
+        <v>39</v>
+      </c>
+      <c r="C97" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="98" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B98" t="s">
+        <v>39</v>
+      </c>
+      <c r="C98" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B99" t="s">
+        <v>39</v>
+      </c>
+      <c r="C99" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="100" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B100" t="s">
+        <v>39</v>
+      </c>
+      <c r="C100" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="101" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B101" t="s">
+        <v>39</v>
+      </c>
+      <c r="C101" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="102" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B102" t="s">
+        <v>39</v>
+      </c>
+      <c r="C102" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="103" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B103" t="s">
+        <v>39</v>
+      </c>
+      <c r="C103" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="104" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B104" t="s">
+        <v>39</v>
+      </c>
+      <c r="C104" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2391,12 +3266,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2538,15 +3410,19 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{960FA430-D311-4659-9843-D5C005D30C23}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0966088-E479-4740-8041-9F3A7F1A6737}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -2570,10 +3446,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A0966088-E479-4740-8041-9F3A7F1A6737}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{960FA430-D311-4659-9843-D5C005D30C23}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>